--- a/cartas.xlsx
+++ b/cartas.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="144">
   <si>
     <t>Planilla de cartas: cómo completarla</t>
   </si>
@@ -358,6 +358,102 @@
   </si>
   <si>
     <t>fotos/diego_santilli.jpg</t>
+  </si>
+  <si>
+    <t>Karina Milei</t>
+  </si>
+  <si>
+    <t>fotos/karina_milei.jpg</t>
+  </si>
+  <si>
+    <t>Martín Lousteau</t>
+  </si>
+  <si>
+    <t>Máximo Kirchner</t>
+  </si>
+  <si>
+    <t>Alberto Fernández</t>
+  </si>
+  <si>
+    <t>Daniel Scioli</t>
+  </si>
+  <si>
+    <t>Gildo Insfrán</t>
+  </si>
+  <si>
+    <t>Juan Schiaretti</t>
+  </si>
+  <si>
+    <t>Jorge Macri</t>
+  </si>
+  <si>
+    <t>Margarita Stolbizer</t>
+  </si>
+  <si>
+    <t>Victoria Villarruel</t>
+  </si>
+  <si>
+    <t>Santiago Caputo</t>
+  </si>
+  <si>
+    <t>Luis Caputo</t>
+  </si>
+  <si>
+    <t>Manuel Adorni</t>
+  </si>
+  <si>
+    <t>Nicolás del Caño</t>
+  </si>
+  <si>
+    <t>Lilia Lemoine</t>
+  </si>
+  <si>
+    <t>fotos/martin_lousteau.jpg</t>
+  </si>
+  <si>
+    <t>fotos/maximo_kirchner.jpg</t>
+  </si>
+  <si>
+    <t>fotos/alberto_fernandez.jpg</t>
+  </si>
+  <si>
+    <t>fotos/daniel_scioli.jpg</t>
+  </si>
+  <si>
+    <t>fotos/gildo_insfran.jpg</t>
+  </si>
+  <si>
+    <t>fotos/juan_schiaretti.jpg</t>
+  </si>
+  <si>
+    <t>fotos/jorge_macri.jpg</t>
+  </si>
+  <si>
+    <t>fotos/margarita_stolbizer.jpg</t>
+  </si>
+  <si>
+    <t>fotos/victoria_villarruel.jpg</t>
+  </si>
+  <si>
+    <t>fotos/santiago_caputo.jpg</t>
+  </si>
+  <si>
+    <t>fotos/luis_caputo.jpg</t>
+  </si>
+  <si>
+    <t>fotos/manuel_adorni.jpg</t>
+  </si>
+  <si>
+    <t>fotos/nicolas_del_cano.jpg</t>
+  </si>
+  <si>
+    <t>fotos/lilia_lemoine.jpg</t>
+  </si>
+  <si>
+    <t>Julio Cobos</t>
+  </si>
+  <si>
+    <t>fotos/julio_cobos.jpg</t>
   </si>
 </sst>
 </file>
@@ -1594,275 +1690,573 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="9" t="str">
+      <c r="F16" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="8">
+        <v>3</v>
+      </c>
+      <c r="H16" s="8">
+        <v>7</v>
+      </c>
+      <c r="I16" s="8">
+        <v>5</v>
+      </c>
+      <c r="J16" s="8">
+        <v>6</v>
+      </c>
+      <c r="K16" s="8">
+        <v>9</v>
+      </c>
+      <c r="L16" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="9" t="str">
+      <c r="F17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="8">
+        <v>3</v>
+      </c>
+      <c r="H17" s="8">
+        <v>8</v>
+      </c>
+      <c r="I17" s="8">
+        <v>4</v>
+      </c>
+      <c r="J17" s="8">
+        <v>7</v>
+      </c>
+      <c r="K17" s="8">
+        <v>7</v>
+      </c>
+      <c r="L17" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="9" t="str">
+      <c r="F18" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="8">
+        <v>3</v>
+      </c>
+      <c r="H18" s="8">
+        <v>7</v>
+      </c>
+      <c r="I18" s="8">
+        <v>5</v>
+      </c>
+      <c r="J18" s="8">
+        <v>6</v>
+      </c>
+      <c r="K18" s="8">
+        <v>7</v>
+      </c>
+      <c r="L18" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="9" t="str">
+      <c r="F19" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="8">
+        <v>3</v>
+      </c>
+      <c r="H19" s="8">
+        <v>9</v>
+      </c>
+      <c r="I19" s="8">
+        <v>4</v>
+      </c>
+      <c r="J19" s="8">
+        <v>6</v>
+      </c>
+      <c r="K19" s="8">
+        <v>7</v>
+      </c>
+      <c r="L19" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="A20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="9" t="str">
+      <c r="F20" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="8">
+        <v>4</v>
+      </c>
+      <c r="H20" s="8">
+        <v>9</v>
+      </c>
+      <c r="I20" s="8">
+        <v>4</v>
+      </c>
+      <c r="J20" s="8">
+        <v>7</v>
+      </c>
+      <c r="K20" s="8">
+        <v>6</v>
+      </c>
+      <c r="L20" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="9" t="str">
+      <c r="F21" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="8">
+        <v>3</v>
+      </c>
+      <c r="H21" s="8">
+        <v>9</v>
+      </c>
+      <c r="I21" s="8">
+        <v>5</v>
+      </c>
+      <c r="J21" s="8">
+        <v>6</v>
+      </c>
+      <c r="K21" s="8">
+        <v>6</v>
+      </c>
+      <c r="L21" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="9" t="str">
+      <c r="F22" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="8">
+        <v>5</v>
+      </c>
+      <c r="H22" s="8">
+        <v>8</v>
+      </c>
+      <c r="I22" s="8">
+        <v>6</v>
+      </c>
+      <c r="J22" s="8">
+        <v>6</v>
+      </c>
+      <c r="K22" s="8">
+        <v>6</v>
+      </c>
+      <c r="L22" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="9" t="str">
+      <c r="F23" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="8">
+        <v>5</v>
+      </c>
+      <c r="H23" s="8">
+        <v>8</v>
+      </c>
+      <c r="I23" s="8">
+        <v>5</v>
+      </c>
+      <c r="J23" s="8">
+        <v>6</v>
+      </c>
+      <c r="K23" s="8">
+        <v>7</v>
+      </c>
+      <c r="L23" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="9" t="str">
+      <c r="F24" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="8">
+        <v>5</v>
+      </c>
+      <c r="H24" s="8">
+        <v>7</v>
+      </c>
+      <c r="I24" s="8">
+        <v>6</v>
+      </c>
+      <c r="J24" s="8">
+        <v>6</v>
+      </c>
+      <c r="K24" s="8">
+        <v>6</v>
+      </c>
+      <c r="L24" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
+      <c r="A25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="9" t="str">
+      <c r="F25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="8">
+        <v>4</v>
+      </c>
+      <c r="H25" s="8">
+        <v>8</v>
+      </c>
+      <c r="I25" s="8">
+        <v>5</v>
+      </c>
+      <c r="J25" s="8">
+        <v>7</v>
+      </c>
+      <c r="K25" s="8">
+        <v>6</v>
+      </c>
+      <c r="L25" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
+      <c r="A26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="9" t="str">
+      <c r="F26" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" s="8">
+        <v>3</v>
+      </c>
+      <c r="H26" s="8">
+        <v>7</v>
+      </c>
+      <c r="I26" s="8">
+        <v>5</v>
+      </c>
+      <c r="J26" s="8">
+        <v>6</v>
+      </c>
+      <c r="K26" s="8">
+        <v>8</v>
+      </c>
+      <c r="L26" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="9" t="str">
+      <c r="F27" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="8">
+        <v>4</v>
+      </c>
+      <c r="H27" s="8">
+        <v>7</v>
+      </c>
+      <c r="I27" s="8">
+        <v>4</v>
+      </c>
+      <c r="J27" s="8">
+        <v>6</v>
+      </c>
+      <c r="K27" s="8">
+        <v>7</v>
+      </c>
+      <c r="L27" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
+      <c r="A28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="9" t="str">
+      <c r="F28" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" s="8">
+        <v>3</v>
+      </c>
+      <c r="H28" s="8">
+        <v>7</v>
+      </c>
+      <c r="I28" s="8">
+        <v>3</v>
+      </c>
+      <c r="J28" s="8">
+        <v>6</v>
+      </c>
+      <c r="K28" s="8">
+        <v>6</v>
+      </c>
+      <c r="L28" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+      <c r="A29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="9" t="str">
+      <c r="F29" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" s="8">
+        <v>5</v>
+      </c>
+      <c r="H29" s="8">
+        <v>6</v>
+      </c>
+      <c r="I29" s="8">
+        <v>5</v>
+      </c>
+      <c r="J29" s="8">
+        <v>6</v>
+      </c>
+      <c r="K29" s="8">
+        <v>6</v>
+      </c>
+      <c r="L29" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
+      <c r="A30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="9" t="str">
+      <c r="F30" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="8">
+        <v>4</v>
+      </c>
+      <c r="H30" s="8">
+        <v>6</v>
+      </c>
+      <c r="I30" s="8">
+        <v>5</v>
+      </c>
+      <c r="J30" s="8">
+        <v>7</v>
+      </c>
+      <c r="K30" s="8">
+        <v>6</v>
+      </c>
+      <c r="L30" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
+      <c r="A31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="9" t="str">
+      <c r="F31" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="8">
+        <v>4</v>
+      </c>
+      <c r="H31" s="8">
+        <v>8</v>
+      </c>
+      <c r="I31" s="8">
+        <v>4</v>
+      </c>
+      <c r="J31" s="8">
+        <v>6</v>
+      </c>
+      <c r="K31" s="8">
+        <v>6</v>
+      </c>
+      <c r="L31" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -4933,7 +5327,7 @@
       </c>
       <c r="E3" s="18">
         <f>COUNTA(Cartas!B2:B201)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4948,7 +5342,7 @@
       </c>
       <c r="E4" s="18">
         <f>MAX(0,(E3-8)/2)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">

--- a/cartas.xlsx
+++ b/cartas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -282,9 +282,6 @@
     <t>fotos/javier_milei.jpg</t>
   </si>
   <si>
-    <t>Cristina Fernández de Kirchner</t>
-  </si>
-  <si>
     <t>fotos/cristina_kirchner.jpg</t>
   </si>
   <si>
@@ -342,9 +339,6 @@
     <t>María Eugenia Vidal</t>
   </si>
   <si>
-    <t>Horacio Rodríguez Larreta</t>
-  </si>
-  <si>
     <t>fotos/axel_kicillof.jpg</t>
   </si>
   <si>
@@ -454,6 +448,12 @@
   </si>
   <si>
     <t>fotos/julio_cobos.jpg</t>
+  </si>
+  <si>
+    <t>Horacio R. Larreta</t>
+  </si>
+  <si>
+    <t>Cristina F. de Kirchner</t>
   </si>
 </sst>
 </file>
@@ -1223,7 +1223,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>64</v>
@@ -1231,7 +1231,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G3" s="8">
         <v>4</v>
@@ -1258,7 +1258,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>84</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="8">
         <v>6</v>
@@ -1295,7 +1295,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>61</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G5" s="8">
         <v>5</v>
@@ -1332,7 +1332,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>53</v>
@@ -1340,7 +1340,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="8">
         <v>5</v>
@@ -1367,7 +1367,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>54</v>
@@ -1379,7 +1379,7 @@
         <v>64</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G7" s="8">
         <v>3</v>
@@ -1406,7 +1406,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>64</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" s="8">
         <v>4</v>
@@ -1443,7 +1443,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>59</v>
@@ -1451,7 +1451,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" s="8">
         <v>4</v>
@@ -1478,7 +1478,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>64</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10" s="8">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>54</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G11" s="8">
         <v>4</v>
@@ -1552,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>64</v>
@@ -1560,7 +1560,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G12" s="8">
         <v>5</v>
@@ -1587,7 +1587,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>59</v>
@@ -1595,7 +1595,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G13" s="8">
         <v>5</v>
@@ -1622,7 +1622,7 @@
         <v>27</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>59</v>
@@ -1630,7 +1630,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G14" s="8">
         <v>5</v>
@@ -1657,7 +1657,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>84</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G15" s="8">
         <v>5</v>
@@ -1694,7 +1694,7 @@
         <v>38</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>84</v>
@@ -1702,7 +1702,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G16" s="8">
         <v>3</v>
@@ -1729,7 +1729,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>61</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G17" s="8">
         <v>3</v>
@@ -1766,7 +1766,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>64</v>
@@ -1774,7 +1774,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G18" s="8">
         <v>3</v>
@@ -1801,7 +1801,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>64</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G19" s="8">
         <v>3</v>
@@ -1838,7 +1838,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>84</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G20" s="8">
         <v>4</v>
@@ -1875,7 +1875,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>64</v>
@@ -1883,7 +1883,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G21" s="8">
         <v>3</v>
@@ -1910,7 +1910,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>54</v>
@@ -1918,7 +1918,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G22" s="8">
         <v>5</v>
@@ -1945,7 +1945,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>59</v>
@@ -1953,7 +1953,7 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G23" s="8">
         <v>5</v>
@@ -1980,7 +1980,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>61</v>
@@ -1988,7 +1988,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G24" s="8">
         <v>5</v>
@@ -2015,7 +2015,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>84</v>
@@ -2023,7 +2023,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G25" s="8">
         <v>4</v>
@@ -2050,7 +2050,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>84</v>
@@ -2058,7 +2058,7 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G26" s="8">
         <v>3</v>
@@ -2085,7 +2085,7 @@
         <v>37</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>84</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G27" s="8">
         <v>4</v>
@@ -2122,7 +2122,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>84</v>
@@ -2130,7 +2130,7 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G28" s="8">
         <v>3</v>
@@ -2157,7 +2157,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>53</v>
@@ -2165,7 +2165,7 @@
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G29" s="8">
         <v>5</v>
@@ -2192,7 +2192,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>84</v>
@@ -2200,7 +2200,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G30" s="8">
         <v>4</v>
@@ -2227,7 +2227,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>61</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G31" s="8">
         <v>4</v>

--- a/cartas.xlsx
+++ b/cartas.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="143">
   <si>
     <t>Planilla de cartas: cómo completarla</t>
   </si>
@@ -129,12 +129,6 @@
     <t>Diputada</t>
   </si>
   <si>
-    <t>Jefe de Gabinete</t>
-  </si>
-  <si>
-    <t>Jefa de Gabinete</t>
-  </si>
-  <si>
     <t>Ministro</t>
   </si>
   <si>
@@ -454,13 +448,16 @@
   </si>
   <si>
     <t>Cristina F. de Kirchner</t>
+  </si>
+  <si>
+    <t>J. de Gabinete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,6 +514,12 @@
       <color rgb="FF666666"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -602,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -632,6 +635,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,10 +1074,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="C21" s="5">
         <v>7</v>
@@ -1081,10 +1085,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" s="5">
         <v>8</v>
@@ -1092,10 +1096,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C23" s="5">
         <v>9</v>
@@ -1103,10 +1107,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" s="5">
         <v>10</v>
@@ -1150,37 +1154,37 @@
         <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,15 +1192,15 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G2" s="8">
         <v>6</v>
@@ -1223,15 +1227,15 @@
         <v>24</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3" s="8">
         <v>4</v>
@@ -1258,17 +1262,17 @@
         <v>32</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4" s="8">
         <v>6</v>
@@ -1295,17 +1299,17 @@
         <v>34</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G5" s="8">
         <v>5</v>
@@ -1332,15 +1336,15 @@
         <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G6" s="8">
         <v>5</v>
@@ -1367,19 +1371,19 @@
         <v>31</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G7" s="8">
         <v>3</v>
@@ -1406,17 +1410,17 @@
         <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8" s="8">
         <v>4</v>
@@ -1443,15 +1447,15 @@
         <v>23</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G9" s="8">
         <v>4</v>
@@ -1478,17 +1482,17 @@
         <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G10" s="8">
         <v>5</v>
@@ -1515,17 +1519,17 @@
         <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G11" s="8">
         <v>4</v>
@@ -1552,15 +1556,15 @@
         <v>27</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G12" s="8">
         <v>5</v>
@@ -1587,15 +1591,15 @@
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="8">
         <v>5</v>
@@ -1622,15 +1626,15 @@
         <v>27</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="8">
         <v>5</v>
@@ -1657,17 +1661,17 @@
         <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="8">
         <v>5</v>
@@ -1691,18 +1695,18 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G16" s="8">
         <v>3</v>
@@ -1729,17 +1733,17 @@
         <v>31</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G17" s="8">
         <v>3</v>
@@ -1766,15 +1770,15 @@
         <v>33</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G18" s="8">
         <v>3</v>
@@ -1801,17 +1805,17 @@
         <v>23</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G19" s="8">
         <v>3</v>
@@ -1838,17 +1842,17 @@
         <v>25</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G20" s="8">
         <v>4</v>
@@ -1875,15 +1879,15 @@
         <v>27</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G21" s="8">
         <v>3</v>
@@ -1910,15 +1914,15 @@
         <v>27</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G22" s="8">
         <v>5</v>
@@ -1945,15 +1949,15 @@
         <v>27</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G23" s="8">
         <v>5</v>
@@ -1980,15 +1984,15 @@
         <v>34</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G24" s="8">
         <v>5</v>
@@ -2015,15 +2019,15 @@
         <v>26</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" s="8">
         <v>4</v>
@@ -2047,18 +2051,18 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G26" s="8">
         <v>3</v>
@@ -2082,20 +2086,20 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G27" s="8">
         <v>4</v>
@@ -2118,19 +2122,19 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>35</v>
+      <c r="A28" s="21" t="s">
+        <v>142</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G28" s="8">
         <v>3</v>
@@ -2157,15 +2161,15 @@
         <v>33</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G29" s="8">
         <v>5</v>
@@ -2192,15 +2196,15 @@
         <v>34</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G30" s="8">
         <v>4</v>
@@ -2227,17 +2231,17 @@
         <v>25</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G31" s="8">
         <v>4</v>
@@ -5150,18 +5154,20 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Cargo" error="Elegí un cargo de la lista." sqref="A2:A201">
-      <formula1>"Presidente,Presidenta,Vicepresidente,Vicepresidenta,Gobernador,Gobernadora,Vicegobernador,Vicegobernadora,Senador,Senadora,Diputado,Diputada,Jefe de Gabinete,Jefa de Gabinete,Ministro,Ministra,Legislador,Legisladora,Asesor,Asesora"</formula1>
-      <formula2>0</formula2>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Cargo" error="Elegí un cargo de la lista." sqref="A3:A201">
+      <formula1>"Presidente,Presidenta,Vicepresidente,Vicepresidenta,Gobernador,Gobernadora,Vicegobernador,Vicegobernadora,Senador,Senadora,Diputado,Diputada,Jefe de Gabinete,J. de Gabinete,Ministro,Ministra,Legislador,Legisladora,Asesor,Asesora"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Atributo" error="Debe ser un número entero de 3 a 10." sqref="G2:K201">
       <formula1>3</formula1>
       <formula2>10</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Cargo" error="Elegí un cargo de la lista." sqref="A2">
+      <formula1>"Presidente,Presidenta,Vicepresidente,Vicepresidenta,Gobernador,Gobernadora,Vicegobernador,Vicegobernadora,Senador,Senadora,Diputado,Diputada,Jefe de Gabinete,J. de Gabinete,Ministro,Ministra,Legislador,Legisladora,Asesor,Asesora"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -5191,61 +5197,61 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5290,25 +5296,25 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2" s="8">
         <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="18">
         <f>SUM(B2:B9)</f>
@@ -5317,13 +5323,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8">
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" s="18">
         <f>COUNTA(Cartas!B2:B201)</f>
@@ -5332,13 +5338,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" s="8">
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" s="18">
         <f>MAX(0,(E3-8)/2)</f>
@@ -5347,13 +5353,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="8">
         <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" s="18" t="str">
         <f>IF(MOD(E3,2)&lt;&gt;0,"Error: la cantidad de políticos debe ser par",IF(E3&lt;8,"Error: hacen falta al menos 8 políticos",IF(E2&lt;E4,"Error: faltan "&amp;(E4-E2)&amp;" tarjetas de eventos","OK")))</f>
@@ -5362,7 +5368,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" s="8">
         <v>8</v>
@@ -5370,18 +5376,18 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B7" s="8">
         <v>8</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B8" s="8">
         <v>8</v>
@@ -5389,7 +5395,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9" s="8">
         <v>8</v>

--- a/cartas.xlsx
+++ b/cartas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -632,10 +632,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -913,82 +913,82 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="21"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="20"/>
+      <c r="C4" s="21"/>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="21"/>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="21"/>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="20"/>
+      <c r="C7" s="21"/>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="20"/>
+      <c r="C8" s="21"/>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="20"/>
+      <c r="C9" s="21"/>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="20"/>
+      <c r="C11" s="21"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1259,107 +1259,103 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="7" t="s">
         <v>57</v>
       </c>
+      <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G4" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="8">
+        <v>9</v>
+      </c>
+      <c r="I4" s="8">
+        <v>5</v>
+      </c>
+      <c r="J4" s="8">
+        <v>7</v>
+      </c>
+      <c r="K4" s="8">
         <v>8</v>
-      </c>
-      <c r="I4" s="8">
-        <v>4</v>
-      </c>
-      <c r="J4" s="8">
-        <v>6</v>
-      </c>
-      <c r="K4" s="8">
-        <v>7</v>
       </c>
       <c r="L4" s="9">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="G5" s="8">
         <v>5</v>
       </c>
       <c r="H5" s="8">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8">
+        <v>5</v>
+      </c>
+      <c r="J5" s="8">
         <v>7</v>
       </c>
-      <c r="I5" s="8">
-        <v>6</v>
-      </c>
-      <c r="J5" s="8">
-        <v>6</v>
-      </c>
       <c r="K5" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L5" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="G6" s="8">
         <v>5</v>
       </c>
       <c r="H6" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" s="8">
         <v>7</v>
       </c>
       <c r="K6" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
@@ -1368,68 +1364,64 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G7" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" s="8">
+        <v>8</v>
+      </c>
+      <c r="I7" s="8">
+        <v>5</v>
+      </c>
+      <c r="J7" s="8">
         <v>7</v>
       </c>
-      <c r="I7" s="8">
-        <v>4</v>
-      </c>
-      <c r="J7" s="8">
+      <c r="K7" s="8">
         <v>6</v>
-      </c>
-      <c r="K7" s="8">
-        <v>7</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G8" s="8">
+        <v>6</v>
+      </c>
+      <c r="H8" s="8">
+        <v>8</v>
+      </c>
+      <c r="I8" s="8">
         <v>4</v>
-      </c>
-      <c r="H8" s="8">
-        <v>6</v>
-      </c>
-      <c r="I8" s="8">
-        <v>5</v>
       </c>
       <c r="J8" s="8">
         <v>6</v>
@@ -1439,211 +1431,213 @@
       </c>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G9" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I9" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8">
         <v>7</v>
       </c>
       <c r="K9" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="G10" s="8">
         <v>5</v>
       </c>
       <c r="H10" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I10" s="8">
         <v>6</v>
       </c>
       <c r="J10" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K10" s="8">
         <v>6</v>
       </c>
       <c r="L10" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>62</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="G11" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="8">
         <v>8</v>
       </c>
       <c r="I11" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8">
         <v>7</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G12" s="8">
         <v>5</v>
       </c>
       <c r="H12" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I12" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L12" s="9">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G13" s="8">
         <v>5</v>
       </c>
       <c r="H13" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I13" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="8">
         <v>7</v>
       </c>
       <c r="K13" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L13" s="9">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G14" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="8">
         <v>8</v>
       </c>
       <c r="I14" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J14" s="8">
         <v>7</v>
@@ -1653,7 +1647,7 @@
       </c>
       <c r="L14" s="9">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1730,26 +1724,26 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G17" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="8">
         <v>4</v>
@@ -1758,107 +1752,105 @@
         <v>7</v>
       </c>
       <c r="K17" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L17" s="9">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G18" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="8">
         <v>7</v>
       </c>
       <c r="I18" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="8">
         <v>6</v>
       </c>
       <c r="K18" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G19" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I19" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="8">
+        <v>7</v>
+      </c>
+      <c r="K19" s="8">
         <v>6</v>
-      </c>
-      <c r="K19" s="8">
-        <v>7</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G20" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" s="8">
         <v>4</v>
@@ -1867,27 +1859,29 @@
         <v>7</v>
       </c>
       <c r="K20" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="7"/>
+      <c r="D21" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21" s="8">
         <v>3</v>
@@ -1896,13 +1890,13 @@
         <v>9</v>
       </c>
       <c r="I21" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="8">
         <v>6</v>
       </c>
       <c r="K21" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="0"/>
@@ -1914,24 +1908,24 @@
         <v>27</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G22" s="8">
+        <v>3</v>
+      </c>
+      <c r="H22" s="8">
+        <v>9</v>
+      </c>
+      <c r="I22" s="8">
         <v>5</v>
-      </c>
-      <c r="H22" s="8">
-        <v>8</v>
-      </c>
-      <c r="I22" s="8">
-        <v>6</v>
       </c>
       <c r="J22" s="8">
         <v>6</v>
@@ -1941,29 +1935,29 @@
       </c>
       <c r="L22" s="9">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G23" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I23" s="8">
         <v>5</v>
@@ -1972,149 +1966,151 @@
         <v>6</v>
       </c>
       <c r="K23" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L23" s="9">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="G24" s="8">
+        <v>4</v>
+      </c>
+      <c r="H24" s="8">
+        <v>6</v>
+      </c>
+      <c r="I24" s="8">
         <v>5</v>
-      </c>
-      <c r="H24" s="8">
-        <v>7</v>
-      </c>
-      <c r="I24" s="8">
-        <v>6</v>
       </c>
       <c r="J24" s="8">
         <v>6</v>
       </c>
       <c r="K24" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L24" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G25" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I25" s="8">
         <v>5</v>
       </c>
       <c r="J25" s="8">
+        <v>6</v>
+      </c>
+      <c r="K25" s="8">
         <v>7</v>
-      </c>
-      <c r="K25" s="8">
-        <v>6</v>
       </c>
       <c r="L25" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="7"/>
+      <c r="D26" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G26" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="8">
         <v>7</v>
       </c>
       <c r="I26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" s="8">
         <v>6</v>
       </c>
       <c r="K26" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L26" s="9">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G27" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="8">
         <v>6</v>
       </c>
       <c r="K27" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L27" s="9">
         <f t="shared" si="0"/>
@@ -2122,11 +2118,11 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>142</v>
+      <c r="A28" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>82</v>
@@ -2134,51 +2130,53 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G28" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="8">
+        <v>6</v>
+      </c>
+      <c r="I28" s="8">
+        <v>5</v>
+      </c>
+      <c r="J28" s="8">
         <v>7</v>
-      </c>
-      <c r="I28" s="8">
-        <v>3</v>
-      </c>
-      <c r="J28" s="8">
-        <v>6</v>
       </c>
       <c r="K28" s="8">
         <v>6</v>
       </c>
       <c r="L28" s="9">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G29" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I29" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" s="8">
         <v>6</v>
@@ -2193,61 +2191,63 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="F30" s="7" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="G30" s="8">
+        <v>3</v>
+      </c>
+      <c r="H30" s="8">
+        <v>7</v>
+      </c>
+      <c r="I30" s="8">
         <v>4</v>
       </c>
-      <c r="H30" s="8">
+      <c r="J30" s="8">
         <v>6</v>
       </c>
-      <c r="I30" s="8">
-        <v>5</v>
-      </c>
-      <c r="J30" s="8">
+      <c r="K30" s="8">
         <v>7</v>
-      </c>
-      <c r="K30" s="8">
-        <v>6</v>
       </c>
       <c r="L30" s="9">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>25</v>
+      <c r="A31" s="20" t="s">
+        <v>142</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>62</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G31" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I31" s="8">
         <v>4</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="L31" s="9">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -5030,7 +5030,7 @@
       <c r="J194" s="8"/>
       <c r="K194" s="8"/>
       <c r="L194" s="9" t="str">
-        <f t="shared" ref="L194:L201" si="6">IF(B194="","",SUM(G194:K194))</f>
+        <f t="shared" ref="L194:L225" si="6">IF(B194="","",SUM(G194:K194))</f>
         <v/>
       </c>
     </row>
@@ -5154,16 +5154,16 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Cargo" error="Elegí un cargo de la lista." sqref="A3:A201">
+  <sortState ref="A2:L31">
+    <sortCondition descending="1" ref="L2:L31"/>
+  </sortState>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Cargo" error="Elegí un cargo de la lista." sqref="A2:A201">
       <formula1>"Presidente,Presidenta,Vicepresidente,Vicepresidenta,Gobernador,Gobernadora,Vicegobernador,Vicegobernadora,Senador,Senadora,Diputado,Diputada,Jefe de Gabinete,J. de Gabinete,Ministro,Ministra,Legislador,Legisladora,Asesor,Asesora"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Atributo" error="Debe ser un número entero de 3 a 10." sqref="G2:K201">
       <formula1>3</formula1>
       <formula2>10</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Cargo" error="Elegí un cargo de la lista." sqref="A2">
-      <formula1>"Presidente,Presidenta,Vicepresidente,Vicepresidenta,Gobernador,Gobernadora,Vicegobernador,Vicegobernadora,Senador,Senadora,Diputado,Diputada,Jefe de Gabinete,J. de Gabinete,Ministro,Ministra,Legislador,Legisladora,Asesor,Asesora"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
